--- a/2-Tests/Lexerow.Core.Tests/10-ExcelFiles/onExcelManyIf.xlsx
+++ b/2-Tests/Lexerow.Core.Tests/10-ExcelFiles/onExcelManyIf.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a990f455bb745add/ProjetsDev/10-Pierlam/Lexerow/Dev/Lexerow/2-Tests/Lexerow.Core.Tests/10-Files/Run/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a990f455bb745add/ProjetsDev/10-Pierlam/Lexerow/Dev/Lexerow/2-Tests/Lexerow.Core.Tests/10-ExcelFiles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="11_2B8C63A238C272CACCFC3B895DC533011B7D74F5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C88BC898-F0D2-4F59-9A13-FA2F553C9272}"/>
+  <xr:revisionPtr revIDLastSave="36" documentId="11_2B8C63A238C272CACCFC3B895DC533011B7D74F5" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FF73E6D3-7876-4F6F-85B1-13E4723234E4}"/>
   <bookViews>
-    <workbookView xWindow="15900" yWindow="3660" windowWidth="13020" windowHeight="9645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="11985" yWindow="4260" windowWidth="16155" windowHeight="6975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="9">
   <si>
     <t>colA</t>
   </si>
@@ -49,6 +49,9 @@
   </si>
   <si>
     <t>A=34, B=blank, C=13</t>
+  </si>
+  <si>
+    <t>A=27, B=blank, C=56</t>
   </si>
 </sst>
 </file>
@@ -67,12 +70,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -87,9 +96,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -105,10 +115,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -374,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D3"/>
+  <dimension ref="A1:D4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="8" customWidth="1"/>
@@ -423,6 +429,20 @@
         <v>7</v>
       </c>
     </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4">
+        <v>27</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="C4">
+        <v>56</v>
+      </c>
+      <c r="D4" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
